--- a/docs/zero-g-tweaks-bundle/sheets/mobs/data/mobs.xlsx
+++ b/docs/zero-g-tweaks-bundle/sheets/mobs/data/mobs.xlsx
@@ -8,21 +8,25 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mobs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_attributes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_drops" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_spawns" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_ai_goals" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_state_transitions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_animations" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_vanilla_bases" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_animation_references" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_attributes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_drops" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_spawns" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_ai_goals" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_state_transitions" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_animations" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'mobs'!$A$1:$Y$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'mob_attributes'!$A$1:$H$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'mob_drops'!$A$1:$I$66</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'mob_spawns'!$A$1:$G$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'mob_ai_goals'!$A$1:$C$171</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'mob_state_transitions'!$A$1:$D$153</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'mob_animations'!$A$1:$D$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'mobs'!$A$1:$Z$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'mob_vanilla_bases'!$A$1:$E$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'mob_animation_references'!$A$1:$D$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'mob_attributes'!$A$1:$H$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'mob_drops'!$A$1:$I$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'mob_spawns'!$A$1:$G$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'mob_ai_goals'!$A$1:$C$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'mob_state_transitions'!$A$1:$D$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'mob_animations'!$A$1:$D$118</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y29"/>
+  <dimension ref="A1:Z29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -449,24 +453,25 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="46" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="46" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="27" customWidth="1" min="19" max="19"/>
-    <col width="33" customWidth="1" min="20" max="20"/>
-    <col width="60" customWidth="1" min="21" max="21"/>
-    <col width="56" customWidth="1" min="22" max="22"/>
-    <col width="60" customWidth="1" min="23" max="23"/>
-    <col width="40" customWidth="1" min="24" max="24"/>
-    <col width="25" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="27" customWidth="1" min="20" max="20"/>
+    <col width="33" customWidth="1" min="21" max="21"/>
+    <col width="60" customWidth="1" min="22" max="22"/>
+    <col width="56" customWidth="1" min="23" max="23"/>
+    <col width="60" customWidth="1" min="24" max="24"/>
+    <col width="40" customWidth="1" min="25" max="25"/>
+    <col width="25" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -507,90 +512,95 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>vanilla_base</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>hitbox_width</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>hitbox_height</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>hitbox_length</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>max_health</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>attack_damage</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>damage_text</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>movement_speed</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>flying_speed</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>follow_range</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>armor</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>knockback_resistance</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>breeding_item</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>immunities</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>behavior</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>spawns_text</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>drops_text</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>loot_table</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>sheet</t>
         </is>
@@ -630,62 +640,67 @@
           <t>Monster</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>minecraft:spider</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0.9</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.5</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>1.1</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>14</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>3</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>3, plus Slowness I for 3 s</t>
         </is>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>0.2</v>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="n">
         <v>16</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
         <is>
           <t>Burrows under Regolith and waits; lunges when a player walks within 3 blocks</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Moon surface, groups of 1–3</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>Crawler Leg 0–2, Regolith Dust 1–3, rare Selenite shard</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/regolith_crawler</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>01_regolith_crawler.png</t>
         </is>
@@ -725,66 +740,71 @@
           <t>Animal + NeutralMob (tameable, saddle + chest like a llama)</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>minecraft:armadillo</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>0.8</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.7</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>20</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>4</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>4 (horn ram) when provoked</t>
         </is>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>0.2</v>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="n">
         <v>16</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>zerog_tweaks:rust_lichen</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
         <is>
           <t>Grazes on Rust Lichen; rams back when hit; tamed beetles with a Ferrox saddle carry a chest</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Mars plains, herds of 2–4</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Beetle Grub 0–1, Ferrox bits 1–2, Rust Shell (armor upgrade)</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/rust_beetle</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>02_rust_beetle.png</t>
         </is>
@@ -824,66 +844,71 @@
           <t>Animal + Shearable</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>minecraft:horse</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>0.9</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>1.8</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>1.3</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>20</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>0.33</v>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="n">
         <v>16</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>zerog_tweaks:starbloom</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
         <is>
           <t>Shear the antlers for 1–2 Starlite; they regrow over 5 minutes. Breeds with Starbloom</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Cerulon Azure Moss plains, herds of 3–5</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Stag Venison 1–3, Crystal Hide 0–2</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/crystal_stag</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>03_crystal_stag.png</t>
         </is>
@@ -923,58 +948,63 @@
           <t>Monster</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>minecraft:endermite</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>0.5</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0.75</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
         <v>8</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2</v>
       </c>
       <c r="M5" t="n">
         <v>2</v>
       </c>
       <c r="N5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" t="n">
         <v>0.33</v>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="n">
         <v>16</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
         <is>
           <t>Swarms in groups; shatters into 2–3 crystal shards on death that deal 1 damage nearby</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Cerulean geodes and crystal caves</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>Crystal shard 1–3 (smelts to Cerulite dust)</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/prismling</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>04_prismling.png</t>
         </is>
@@ -1014,66 +1044,71 @@
           <t>Monster</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>minecraft:wolf</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>0.7</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>0.9</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>1.2</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>18</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>4</v>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>4, sets target on fire for 2 s</t>
         </is>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>0.33</v>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="n">
         <v>24</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr">
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
         <is>
           <t>fire; lava</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Hunts in packs of 3–5; circles, then lunges together. Immune to fire</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Skarn Ember Crust fields</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Cinder pelt, Emberite 0–2</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/cinder_hound</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>05_cinder_hound.png</t>
         </is>
@@ -1113,64 +1148,69 @@
           <t>Monster + ServerBossEvent (pale cyan)</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>minecraft:vindicator</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>2.4</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
         <v>120</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>9</v>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>9; glaive sweep 12 and Slowness II</t>
         </is>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>0.2</v>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="n">
         <v>32</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>10</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>0.8</v>
       </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr">
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
         <is>
           <t>freezing</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Guards the largest wrecks. Phase 2 at half health: summons 2 Rime Stalkers and an ice wall ring</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>One per large wreck on Eidolon; does not respawn</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>Wraithsteel Ingots 3–5, Frost Warden Helm (trophy), Remnant Shard</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/frost_warden</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>06_frost_warden.png</t>
         </is>
@@ -1210,66 +1250,71 @@
           <t>FlyingMob / Monster with FlyingMoveControl (Blaze/Vex pattern)</t>
         </is>
       </c>
-      <c r="H8" t="n">
-        <v>0.5</v>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>minecraft:vex</t>
+        </is>
       </c>
       <c r="I8" t="n">
         <v>0.5</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
+      <c r="J8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
         <v>6</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>3</v>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>3 fire, or a small fireball at range</t>
         </is>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>0.33</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>0.6</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>16</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr">
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
         <is>
           <t>fire; lava</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Swarms around Flare Vents; bursts into flame when a vent erupts. Water puts it out instantly</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Solvane near Flare Vents, swarms of 4–8</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>Fusion Dust 0–1, Solar Spark</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/flare_sprite</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>07_flare_sprite.png</t>
         </is>
@@ -1309,64 +1354,69 @@
           <t>Monster + ServerBossEvent (yellow)</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>minecraft:iron_golem</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>2.6</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>2.9</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
         <v>200</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>14</v>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>14 slam; ground wave sets fire in a line</t>
         </is>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>0.15</v>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="n">
         <v>32</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>20</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>1</v>
       </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr">
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
         <is>
           <t>fire; lava</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Wakes when a player steps on its Sunspot Rock plateau. Core opens to take damage after each slam</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>One per Solvane plateau structure</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>Astrium 4–6, Coronite 6–10, Colossus Core (Fusion Reactor upgrade)</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/sun_colossus</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>08_sun_colossus.png</t>
         </is>
@@ -1406,60 +1456,65 @@
           <t>Monster</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>minecraft:silverfish</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>1.2</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>1.9</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="n">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
         <v>40</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>8</v>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>8; can swallow and hold a player for 2 s</t>
         </is>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>0.33</v>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="n">
         <v>24</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>4</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
         <is>
           <t>Travels under sand shown as a moving ripple; bursts up under players who stand still</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Desert wastelands in every galaxy</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>Burrower Steak 1–3, Burrower Scale, Star Map Fragment (rare)</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/dune_burrower</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>09_dune_burrower.png</t>
         </is>
@@ -1499,68 +1554,73 @@
           <t>Animal + NeutralMob + ItemSteerable (Strider pattern)</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>minecraft:strider</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>1.9</v>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
         <v>30</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>6</v>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>6 stomp</t>
         </is>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>0.25</v>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="n">
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="n">
         <v>16</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
         <is>
           <t>zerog_tweaks:cinder_cap</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>fire; lava</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Wades across lava lakes; rideable with a saddle, making it the lava crossing mount</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Volcanic wastelands</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>Heatproof Plating (rare), ash 1–3</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/ash_strider</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>10_ash_strider.png</t>
         </is>
@@ -1600,64 +1660,69 @@
           <t>Monster</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>minecraft:ocelot</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>0.8</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
         <v>24</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>5</v>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>5, plus Freezing</t>
         </is>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>0.33</v>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="n">
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="n">
         <v>24</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr">
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
         <is>
           <t>freezing</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Stalks from behind; only visible within 8 blocks during blizzards</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Frozen wastelands; summoned by the Frost Warden</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>Cryo Core (rare), Frost pelt</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/rime_stalker</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>11_rime_stalker.png</t>
         </is>
@@ -1697,66 +1762,71 @@
           <t>Monster (amphibious, Drowned-like navigation)</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>minecraft:axolotl</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>0.7</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>1.4</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>28</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>5</v>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>5, and spits acid (Poison II, 4 s)</t>
         </is>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>0.2</v>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="n">
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="n">
         <v>16</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr">
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
         <is>
           <t>zerog_tweaks:acid; poison</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Lies submerged in Acid with only eyes showing</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Toxic wastelands</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>Lurker Leg 1–2, Venom Gland 0–1, Neutralizer (rare)</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/bog_lurker</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>12_bog_lurker.png</t>
         </is>
@@ -1796,62 +1866,67 @@
           <t>FlyingMob + NeutralMob (Ghast-like drift, small)</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>minecraft:ghast</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>0.8</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>1.4</v>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="n">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
         <v>20</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>4</v>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>None unless hit, then 4</t>
         </is>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>0.2</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>0.3</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>16</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr">
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
         <is>
           <t>Floats over craters; drops Meteorite Fragments as it drifts. Attacking one makes nearby drifters swarm</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Barren wastelands</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>Stardust 1–2, Meteorite Fragment</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/crater_drifter</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>13_crater_drifter.png</t>
         </is>
@@ -1891,60 +1966,65 @@
           <t>Monster + ServerBossEvent (cyan) ; no natural spawn</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>minecraft:blaze</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>2</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>2.4</v>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="n">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
         <v>300</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>10</v>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Light beams 10; shard spin 8</t>
         </is>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>0.2</v>
       </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="n">
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="n">
         <v>48</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>15</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>1</v>
       </c>
-      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr">
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
         <is>
           <t>1: beams bounce off the orbiting shards. 2: shards break loose and circle the arena. 3: core cracks open, and hits to the heart light deal double</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Crystal amphitheater on Galaxy 2's key world</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>Galaxy 3 gate key, Cerulite 4–6, Sentinel Prism (T3 lens upgrade)</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/prism_sentinel</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>14_prism_sentinel.png</t>
         </is>
@@ -1984,62 +2064,67 @@
           <t>Monster + ServerBossEvent (purple) ; no natural spawn</t>
         </is>
       </c>
-      <c r="H16" t="n">
-        <v>2.4</v>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>minecraft:ravager</t>
+        </is>
       </c>
       <c r="I16" t="n">
         <v>2.4</v>
       </c>
       <c r="J16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K16" t="n">
         <v>3.2</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>450</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>16</v>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Claw 16; rift pull drags you toward the rift</t>
         </is>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>0.25</v>
       </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="n">
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="n">
         <v>48</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>18</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>1</v>
       </c>
-      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr">
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
         <is>
           <t>1: charges and claws. 2: rift pulls chunks of the arena into the void. 3: spines fire void shards</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Fractured island over the void on Galaxy 3's key world</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>Galaxy 4 gate key, Skarnite 4–6, Rift Heart</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/rift_tyrant</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>15_rift_tyrant.png</t>
         </is>
@@ -2079,60 +2164,65 @@
           <t>Monster + ServerBossEvent (white) ; no natural spawn</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>minecraft:vindicator</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>0.9</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>2.6</v>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
         <v>400</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>13</v>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Cutlass 13; lantern beam chills</t>
         </is>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>0.25</v>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="n">
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="n">
         <v>48</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>14</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>0.9</v>
       </c>
-      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr">
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
         <is>
           <t>1: duels with the cutlass. 2: calls Hollow Crewmen. 3: fleet lantern freezes the deck</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Flagship deck on Galaxy 4's key world</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>Galaxy 5 gate key, Eidolite 4–6; Captain's Lantern if spared</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/eidolon_captain</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>16_eidolon_captain.png</t>
         </is>
@@ -2172,62 +2262,67 @@
           <t>FlyingMob + ServerBossEvent (yellow-&gt;white) ; no natural spawn</t>
         </is>
       </c>
-      <c r="H18" t="n">
-        <v>3.6</v>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>minecraft:wither</t>
+        </is>
       </c>
       <c r="I18" t="n">
         <v>3.6</v>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
+      <c r="J18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
         <v>900</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>20</v>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Solar flare 20; falling stars 12</t>
         </is>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>0.2</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>0.4</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>64</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>20</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>1</v>
       </c>
-      <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr">
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
         <is>
           <t>1: Vael fights from the surface. 2: corona rays sweep the arena. 3: the star collapses, the core opens and the arena shrinks</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Floating ring platform above Solvane</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>Heart of Solvane, Solvanite 6–8, T6 crown</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/dying_star</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>17_dying_star.png</t>
         </is>
@@ -2267,64 +2362,69 @@
           <t>Animal (Rabbit pattern: JumpControl + RabbitMoveControl)</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>minecraft:rabbit</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>0.5</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>0.6</v>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
         <v>6</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>0.25</v>
       </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="n">
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="n">
         <v>16</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr">
         <is>
           <t>zerog_tweaks:lunar_lichen</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr">
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
         <is>
           <t>Hops up to 4 blocks high in Moon gravity; flees when hit</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Moon surface, groups of 2–4</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>Hopper Meat 0–2, Hopper Fluff 1–2</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/moon_hopper</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>18_moon_hopper.png</t>
         </is>
@@ -2364,64 +2464,69 @@
           <t>Animal (Cow pattern)</t>
         </is>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>minecraft:cow</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>1.3</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>1.4</v>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
         <v>24</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>0</v>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>0.25</v>
       </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="n">
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="n">
         <v>16</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="inlineStr">
         <is>
           <t>zerog_tweaks:rust_tuber</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr">
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
         <is>
           <t>Grazes in herds; the whole herd stampedes if one is hit</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Mars plains, herds of 3–6</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>Grazer Steak 1–3, Grazer Hide 0–2</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/dust_grazer</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>19_dust_grazer.png</t>
         </is>
@@ -2461,64 +2566,69 @@
           <t>Animal (Chicken-like)</t>
         </is>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>minecraft:chicken</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>0.4</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>0.8</v>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="n">
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="n">
         <v>4</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>0</v>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>0.25</v>
       </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="n">
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="n">
         <v>16</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr">
         <is>
           <t>zerog_tweaks:skyberries</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr">
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
         <is>
           <t>Glides slowly when falling; lays a Blue Egg every 5–10 minutes</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Cerulon moss plains and Shardwood forests</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>Raw Fowl 1, Azure Feather 0–2</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/azure_fowl</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>20_azure_fowl.png</t>
         </is>
@@ -2558,60 +2668,65 @@
           <t>AbstractSchoolingFish</t>
         </is>
       </c>
-      <c r="H22" t="n">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>minecraft:tropical_fish</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
         <v>0.5</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>0.4</v>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="n">
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="n">
         <v>3</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>0.33</v>
       </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="n">
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="n">
         <v>16</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
       <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr">
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
         <is>
           <t>Schools of 4–8; lights the water around it at night</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>Cerulon lakes and oceans</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>Glimmerfish 1, Glimmer Scale 0–1 (rare)</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/glimmerfish</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>21_glimmerfish.png</t>
         </is>
@@ -2651,70 +2766,75 @@
           <t>Animal + NeutralMob</t>
         </is>
       </c>
-      <c r="H23" t="n">
-        <v>0.9</v>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>minecraft:hoglin</t>
+        </is>
       </c>
       <c r="I23" t="n">
         <v>0.9</v>
       </c>
       <c r="J23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K23" t="n">
         <v>1.3</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>26</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>6</v>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>6 charge, only when provoked</t>
         </is>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>0.25</v>
       </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="n">
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="n">
         <v>16</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="inlineStr">
         <is>
           <t>zerog_tweaks:cinder_cap</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>fire</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>Roots through Slag; charges if hit or if you get too close to its young</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>Skarn slag fields</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>Boar Chop 1–3, Boar Tusk 0–1</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/slag_boar</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>22_slag_boar.png</t>
         </is>
@@ -2754,66 +2874,71 @@
           <t>Monster (glides, not full flight)</t>
         </is>
       </c>
-      <c r="H24" t="n">
-        <v>0.6</v>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>minecraft:parrot</t>
+        </is>
       </c>
       <c r="I24" t="n">
         <v>0.6</v>
       </c>
       <c r="J24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>16</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>3</v>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>3 bite; spits a fire bolt (3 + fire)</t>
         </is>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>0.25</v>
       </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="n">
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="n">
         <v>16</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr">
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
         <is>
           <t>fire</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>Glides between ledges; guards Emberite veins</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>Skarn lava contact zones</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>Scorch Tail 1, Scorch Scale 0–2</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/scorch_wyrmling</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>23_scorch_wyrmling.png</t>
         </is>
@@ -2853,68 +2978,73 @@
           <t>Animal + Shearable (Sheep + Cow pattern)</t>
         </is>
       </c>
-      <c r="H25" t="n">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>minecraft:cow</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>1.4</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>1.7</v>
       </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="n">
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="n">
         <v>30</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>0.2</v>
       </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="n">
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="n">
         <v>16</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="inlineStr">
         <is>
           <t>zerog_tweaks:frostfern</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>freezing</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>Shear for Yak Wool; milk with a glass bottle for Frost Milk. Shelters calves in blizzards</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>Eidolon glaciers, herds of 2–4</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>Yak Meat 1–3, Yak Wool 1–2</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/frost_yak</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>24_frost_yak.png</t>
         </is>
@@ -2954,66 +3084,71 @@
           <t>Monster</t>
         </is>
       </c>
-      <c r="H26" t="n">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>minecraft:silverfish</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>0.6</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>0.4</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>1.2</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>14</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>2</v>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>2 and latches on: Hunger II while attached</t>
         </is>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>0.25</v>
       </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="n">
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="n">
         <v>16</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr">
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
         <is>
           <t>freezing</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>Hides under Snowpack; shake it off by sprinting or hitting it</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>Eidolon snowfields and wreck interiors</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>Leech Gel 1–3</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/ice_leech</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>25_ice_leech.png</t>
         </is>
@@ -3053,68 +3188,73 @@
           <t>Animal + NeutralMob</t>
         </is>
       </c>
-      <c r="H27" t="n">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>minecraft:spider</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
         <v>0.9</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>0.5</v>
       </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="n">
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="n">
         <v>12</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>3</v>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>3 pinch, only when attacked</t>
         </is>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>0.25</v>
       </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="n">
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="n">
         <v>16</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="inlineStr">
         <is>
           <t>zerog_tweaks:pyrefruit</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>fire; zerog_tweaks:corona_crust</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>Walks sideways; basks on Sunspot Rock and is immune to heat</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>Solvane Sunspot Rock shores</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>Gildcrab Meat 1–2, Gildcrab Shell 0–1</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/gildcrab</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>26_gildcrab.png</t>
         </is>
@@ -3154,62 +3294,67 @@
           <t>WaterAnimal/Monster with SmoothSwimmingMoveControl (Guardian/Drowned nav)</t>
         </is>
       </c>
-      <c r="H28" t="n">
-        <v>0.6</v>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>minecraft:dolphin</t>
+        </is>
       </c>
       <c r="I28" t="n">
         <v>0.6</v>
       </c>
       <c r="J28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K28" t="n">
         <v>1.8</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>22</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>6</v>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>6 bite; pulls you down 2 blocks</t>
         </is>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>0.33</v>
       </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="n">
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="n">
         <v>16</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr">
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
         <is>
           <t>Lurks in trenches; follows light sources</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>Ocean wastelands in every galaxy (tinted)</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>Eel Fillet 1–2, Eel Skin 0–1</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/deep_eel</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>27_deep_eel.png</t>
         </is>
@@ -3249,76 +3394,3483 @@
           <t>Monster (Spider-like)</t>
         </is>
       </c>
-      <c r="H29" t="n">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>minecraft:spider</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
         <v>1</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>0.6</v>
       </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="n">
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="n">
         <v>16</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>3</v>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>3 and Poison I for 4 s</t>
         </is>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>0.33</v>
       </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="n">
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="n">
         <v>16</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr">
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
         <is>
           <t>poison</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>Buries itself in Dunesand; bursts out in groups of 2–3</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>Desert wastelands (tinted)</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>Skitter Leg 1–2, Skitter Carapace 0–1, Venom Gland 0–1</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/sand_skitter</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>28_sand_skitter.png</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y29"/>
+  <autoFilter ref="A1:Z29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>mob</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>vanilla_base</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>also</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>rig</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>regolith_crawler</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Regolith Crawler</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>minecraft:spider</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>minecraft:silverfish</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Spider layout: low body, head in front, legs in pairs splayed sideways (we have 3 pairs instead of 4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>rust_beetle</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rust Beetle</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>minecraft:armadillo</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>minecraft:llama minecraft:goat</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Armadillo layout: domed shell over a small body, short legs, head low at the front. Horn on the head bone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>crystal_stag</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Crystal Stag</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>minecraft:horse</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>minecraft:goat</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Horse layout: long legs, neck and head raised in front, tail at the back. Antlers sit on the head bone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>prismling</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Prismling</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>minecraft:endermite</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>minecraft:silverfish</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Endermite layout: small body segments close to the ground; crystal spikes ride the body bone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cinder_hound</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cinder Hound</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>minecraft:wolf</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Wolf layout exactly: body, mane, head with snout and ears, 4 legs, tail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>frost_warden</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Frost Warden</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>minecraft:vindicator</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>minecraft:warden minecraft:iron_golem</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Vindicator (illager) layout: head, body, 2 arms, 2 legs; the glaive is held in the right arm like the vindicator axe. Walk weight from the warden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>flare_sprite</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Flare Sprite</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>minecraft:vex</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>minecraft:blaze</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Vex layout: small flying humanoid with two wings, no legs used.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sun_colossus</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sun Colossus</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>minecraft:iron_golem</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>minecraft:warden</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Iron golem layout: big body, small head, long arms, 2 legs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>dune_burrower</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dune Burrower</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>minecraft:silverfish</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>minecraft:sniffer minecraft:warden</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Silverfish layout scaled up: a chain of segments with a big head segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ash_strider</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ash Strider</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>minecraft:strider</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Strider layout exactly: body block on two long legs, bristles on the body.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>rime_stalker</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rime Stalker</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>minecraft:ocelot</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>minecraft:wolf</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Ocelot/cat layout: long body, 4 legs, long tail, head with ears. Spines on the body bone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>bog_lurker</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Bog Lurker</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>minecraft:axolotl</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>minecraft:frog</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Axolotl layout scaled up: long flat body, 4 short legs, tail, wide head.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>crater_drifter</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Crater Drifter</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>minecraft:ghast</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>minecraft:allay</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Ghast layout, small: floating body with hanging tendrils.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>prism_sentinel</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Prism Sentinel</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>minecraft:blaze</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>minecraft:guardian minecraft:elder_guardian</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Blaze layout: floating core with an orbit bone for the shards (like the blaze rods), no legs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>rift_tyrant</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rift Tyrant</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>minecraft:ravager</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>minecraft:warden</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ravager layout: huge body, heavy head with jaw, 4 legs. Spines on the body bone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>eidolon_captain</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Eidolon Captain</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>minecraft:vindicator</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>minecraft:evoker minecraft:vex</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Vindicator (illager) layout: the cutlass in the right arm, the lantern in the left. Rendered see-through like a vex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>dying_star</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>The Dying Star</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>minecraft:wither</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>minecraft:blaze minecraft:ender_dragon</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Wither-style floating boss: core body with ray bones orbiting like blaze rods; Vael is a bone on top.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>moon_hopper</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Moon Hopper</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>minecraft:rabbit</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Rabbit layout exactly: body, head, long ears, big hind feet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>dust_grazer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dust Grazer</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>minecraft:cow</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>minecraft:goat</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Cow layout: body, head with curved horns, 4 legs; the mane is an extra layer on the body.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>azure_fowl</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Azure Fowl</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>minecraft:chicken</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>minecraft:parrot</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Chicken layout exactly: body, head, beak, wings, two legs. Crest on the head bone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>glimmerfish</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Glimmerfish</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>minecraft:tropical_fish</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>minecraft:salmon</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Tropical fish layout: body, tail fin, top and side fins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>slag_boar</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Slag Boar</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>minecraft:hoglin</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Hoglin layout exactly: big head with tusks, body, 4 legs. Our tail is an extra bone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>scorch_wyrmling</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Scorch Wyrmling</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>minecraft:parrot</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>minecraft:phantom minecraft:blaze</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Parrot layout: small body that walks and glides, two wings, tail; head on a short neck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>frost_yak</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Frost Yak</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>minecraft:cow</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>minecraft:sheep minecraft:llama</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Cow layout: big body, head with horns, 4 legs. Wool is an extra layer on the body, like the sheep wool layer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ice_leech</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Ice Leech</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>minecraft:silverfish</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Silverfish layout: a chain of body segments, each its own bone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>gildcrab</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Gildcrab</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>minecraft:spider</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>minecraft:armadillo</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Spider layout turned sideways: body wider than long, legs splayed left and right; pincers are extra front arm bones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>deep_eel</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Deep Eel</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>minecraft:dolphin</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>minecraft:guardian minecraft:drowned</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Dolphin layout stretched into an eel: head, body segments, tail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sand_skitter</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Sand Skitter</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>minecraft:spider</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>minecraft:silverfish</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Spider layout: body and head low, 6-8 splayed legs; the stinger tail is an extra bone chain arched over the back.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E29"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D118"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>mob</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>animation</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>copy_from</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>exists</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>regolith_crawler</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>animation.regolith_crawler.idle</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>spider idle (legs still, slight body sway)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>regolith_crawler</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>animation.regolith_crawler.walk</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>spider walk (alternating leg pairs)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>regolith_crawler</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>animation.regolith_crawler.burrow</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>silverfish hiding in a block: sink down in 20 ticks</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>regolith_crawler</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>animation.regolith_crawler.emerge</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>reverse of burrow, then spider-style rear-up</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>regolith_crawler</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>animation.regolith_crawler.lunge</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>spider leap (LeapAtTargetGoal arc)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>regolith_crawler</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>animation.regolith_crawler.death</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>vanilla death tip-over</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>rust_beetle</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>animation.rust_beetle.idle</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>armadillo idle</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>rust_beetle</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>animation.rust_beetle.walk</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>armadillo walk</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>rust_beetle</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>animation.rust_beetle.ram</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>goat ram (head down, charge)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>rust_beetle</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>animation.rust_beetle.hop</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>rabbit hop timing, with the shell split open like elytra</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>rust_beetle</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>animation.rust_beetle.graze</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>sheep eat-grass head dip</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>crystal_stag</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>animation.crystal_stag.idle</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>horse idle (tail swish, head bob)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>crystal_stag</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>animation.crystal_stag.walk</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>horse walk</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>crystal_stag</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>animation.crystal_stag.run</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>horse gallop</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>crystal_stag</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>animation.crystal_stag.graze</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>horse eating (neck down)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>prismling</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>animation.prismling.idle</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>endermite idle wiggle</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>prismling</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>animation.prismling.walk</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>endermite skitter</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>prismling</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>animation.prismling.attack</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>silverfish lunge bite</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>prismling</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>animation.prismling.shatter</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>custom: scale to 0 with shard particles</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cinder_hound</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>animation.cinder_hound.idle</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>wolf idle (tail wag)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cinder_hound</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>animation.cinder_hound.walk</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>wolf walk</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cinder_hound</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>animation.cinder_hound.run</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>wolf run</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cinder_hound</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>animation.cinder_hound.lunge</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>wolf LeapAtTarget pounce</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cinder_hound</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>animation.cinder_hound.bite</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>wolf attack snap</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>frost_warden</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>animation.frost_warden.idle</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>vindicator idle, arms crossed or weapon held</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>frost_warden</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>animation.frost_warden.walk</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>warden heavy walk</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>frost_warden</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>animation.frost_warden.sweep</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>vindicator axe swing, widened into a sweep</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>frost_warden</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>animation.frost_warden.summon</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>evoker spell-cast (arms raised)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>frost_warden</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>animation.frost_warden.death</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>vanilla death tip-over</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>flare_sprite</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>animation.flare_sprite.fly</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>vex flying (wing flicker, hover bob)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>flare_sprite</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>animation.flare_sprite.attack</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>blaze fireball charge (glow up, then shoot)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>sun_colossus</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>animation.sun_colossus.dormant</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>custom: crouched, still</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>sun_colossus</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>animation.sun_colossus.wake</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>warden emerge (rising out of the ground)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>sun_colossus</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>animation.sun_colossus.walk</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>iron golem walk</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>sun_colossus</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>animation.sun_colossus.slam</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>iron golem attack (both arms swing down)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>sun_colossus</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>animation.sun_colossus.core_open</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>custom: chest plates swing open</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>sun_colossus</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>animation.sun_colossus.death</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>vanilla death tip-over</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>dune_burrower</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>animation.dune_burrower.burrow</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>warden dig (sinking)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>dune_burrower</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>animation.dune_burrower.burst</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>warden emerge, fast</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>dune_burrower</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>animation.dune_burrower.swallow</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>custom: head segment opens and closes</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>dune_burrower</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>animation.dune_burrower.walk</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>silverfish crawl</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>dune_burrower</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>animation.dune_burrower.attack</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>silverfish lunge</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ash_strider</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>animation.ash_strider.idle</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>strider idle</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ash_strider</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>animation.ash_strider.walk</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>strider walk (also on lava)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ash_strider</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>animation.ash_strider.stomp</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>strider leg stamp, emphasized</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>rime_stalker</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>animation.rime_stalker.idle</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ocelot idle</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>rime_stalker</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>animation.rime_stalker.walk</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ocelot sneak-walk (crouched stalk)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>rime_stalker</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>animation.rime_stalker.pounce</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ocelot/cat pounce</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>rime_stalker</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>animation.rime_stalker.attack</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>wolf bite</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>bog_lurker</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>animation.bog_lurker.idle</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>axolotl idle (lying still)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>bog_lurker</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>animation.bog_lurker.walk</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>axolotl walk on land</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>bog_lurker</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>animation.bog_lurker.swim</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>axolotl swim</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>bog_lurker</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>animation.bog_lurker.spit</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>llama spit head jerk</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>crater_drifter</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>animation.crater_drifter.float</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ghast idle (tendril sway, bob)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>crater_drifter</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>animation.crater_drifter.attack</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ghast shoot (body flinch forward)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>prism_sentinel</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>animation.prism_sentinel.idle</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>blaze idle (rods orbit), 4 s loop</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>prism_sentinel</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>animation.prism_sentinel.beam</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>guardian laser charge and fire</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>prism_sentinel</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>animation.prism_sentinel.shard_spin</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>blaze rods spinning fast</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>prism_sentinel</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>animation.prism_sentinel.core_open</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>custom: core plates open</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>prism_sentinel</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>animation.prism_sentinel.death</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>custom: shards fall, core cracks</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>rift_tyrant</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>animation.rift_tyrant.idle</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ravager idle</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>rift_tyrant</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>animation.rift_tyrant.walk</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ravager walk</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>rift_tyrant</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>animation.rift_tyrant.charge</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ravager charge</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>rift_tyrant</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>animation.rift_tyrant.claw</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ravager bite, turned into a swipe</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>rift_tyrant</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>animation.rift_tyrant.roar</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ravager roar</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>rift_tyrant</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>animation.rift_tyrant.shard_volley</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>warden sonic boom wind-up</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>rift_tyrant</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>animation.rift_tyrant.death</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>vanilla death tip-over</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>eidolon_captain</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>animation.eidolon_captain.idle</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>vindicator idle</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>eidolon_captain</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>animation.eidolon_captain.walk</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>vindicator walk</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>eidolon_captain</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>animation.eidolon_captain.slash</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>vindicator axe swing</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>eidolon_captain</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>animation.eidolon_captain.summon</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>evoker summon (arms raised)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>eidolon_captain</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>animation.eidolon_captain.lantern</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>evoker spell-cast holding the lantern high</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>eidolon_captain</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>animation.eidolon_captain.yield</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>custom: kneels, sword down</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>eidolon_captain</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>animation.eidolon_captain.death</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>custom: fades out</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>dying_star</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>animation.dying_star.idle</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>wither hover and blaze-rod rotation</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>dying_star</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>animation.dying_star.flare</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>wither charge-up and blast</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>dying_star</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>animation.dying_star.sweep</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ender dragon breath sweep</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>dying_star</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>animation.dying_star.collapse</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>wither spawn in reverse (shrinks)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>dying_star</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>animation.dying_star.death</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ender dragon death beams</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>moon_hopper</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>animation.moon_hopper.idle</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>rabbit idle (nose twitch)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>moon_hopper</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>animation.moon_hopper.hop</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>rabbit jump (scale the height ×2 for Moon gravity)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>moon_hopper</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>animation.moon_hopper.graze</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>rabbit eating</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>dust_grazer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>animation.dust_grazer.idle</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>cow idle</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>dust_grazer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>animation.dust_grazer.walk</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>cow walk</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>dust_grazer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>animation.dust_grazer.run</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>cow panic run</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>dust_grazer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>animation.dust_grazer.graze</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>sheep eat-grass</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>azure_fowl</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>animation.azure_fowl.idle</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>chicken idle (head peck)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>azure_fowl</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>animation.azure_fowl.walk</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>chicken walk</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>azure_fowl</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>animation.azure_fowl.glide</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>chicken falling (wings flap slowly, fall slowed)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>azure_fowl</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>animation.azure_fowl.flap</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>chicken wing flap</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>glimmerfish</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>animation.glimmerfish.swim</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>tropical fish tail wave</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>glimmerfish</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>animation.glimmerfish.flop</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>fish flopping on land</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>slag_boar</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>animation.slag_boar.idle</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>hoglin idle</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>slag_boar</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>animation.slag_boar.walk</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>hoglin walk</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>slag_boar</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>animation.slag_boar.charge</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>hoglin head-toss attack while running</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>slag_boar</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>animation.slag_boar.root</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>hoglin head down, swinging side to side</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>scorch_wyrmling</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>animation.scorch_wyrmling.idle</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>parrot idle</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>scorch_wyrmling</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>animation.scorch_wyrmling.walk</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>parrot walk</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>scorch_wyrmling</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>animation.scorch_wyrmling.glide</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>phantom glide (wings out, slow flap)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>scorch_wyrmling</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>animation.scorch_wyrmling.spit</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>llama spit head jerk (projectile like a blaze fireball)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>scorch_wyrmling</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>animation.scorch_wyrmling.bite</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>parrot peck, scaled up</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>frost_yak</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>animation.frost_yak.idle</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>cow idle</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>frost_yak</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>animation.frost_yak.walk</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>cow walk</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>frost_yak</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>animation.frost_yak.graze</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>sheep eat-grass</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>ice_leech</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>animation.ice_leech.idle</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>silverfish idle</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>ice_leech</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>animation.ice_leech.crawl</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>silverfish crawl (segment wave)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>ice_leech</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>animation.ice_leech.latch</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>custom: curl around, ride the player like a chicken jockey</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>gildcrab</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>animation.gildcrab.idle</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>spider idle</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>gildcrab</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>animation.gildcrab.walk_sideways</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>spider walk played on the X axis</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>gildcrab</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>animation.gildcrab.pinch</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>custom pincer snap</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>gildcrab</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>animation.gildcrab.bask</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>armadillo settled pose</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>deep_eel</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>animation.deep_eel.swim</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>dolphin swim wave, carried down each segment</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>deep_eel</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>animation.deep_eel.bite</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>guardian snap, with a pull-down</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>sand_skitter</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>animation.sand_skitter.idle</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>spider idle</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>sand_skitter</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>animation.sand_skitter.walk</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>spider walk</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>sand_skitter</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>animation.sand_skitter.burst</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>silverfish popping out of a block</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>sand_skitter</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>animation.sand_skitter.sting</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>custom: tail arcs over and forward</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D118"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4119,7 +7671,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6857,7 +10409,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7600,7 +11152,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10187,7 +13739,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13554,7 +17106,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/zero-g-tweaks-bundle/sheets/mobs/data/mobs.xlsx
+++ b/docs/zero-g-tweaks-bundle/sheets/mobs/data/mobs.xlsx
@@ -8,25 +8,27 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mobs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_vanilla_bases" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_animation_references" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_attributes" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_drops" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_spawns" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_ai_goals" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_state_transitions" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_animations" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_eye_styles" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_vanilla_bases" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_animation_references" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_attributes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_drops" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_spawns" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_ai_goals" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_state_transitions" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mob_animations" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'mobs'!$A$1:$Z$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'mob_vanilla_bases'!$A$1:$E$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'mob_animation_references'!$A$1:$D$118</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'mob_attributes'!$A$1:$H$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'mob_drops'!$A$1:$I$66</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'mob_spawns'!$A$1:$G$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'mob_ai_goals'!$A$1:$C$171</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'mob_state_transitions'!$A$1:$D$153</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'mob_animations'!$A$1:$D$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'mobs'!$A$1:$AB$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'mob_eye_styles'!$A$1:$G$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'mob_vanilla_bases'!$A$1:$E$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'mob_animation_references'!$A$1:$D$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'mob_attributes'!$A$1:$H$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'mob_drops'!$A$1:$I$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'mob_spawns'!$A$1:$G$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'mob_ai_goals'!$A$1:$C$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'mob_state_transitions'!$A$1:$D$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'mob_animations'!$A$1:$D$118</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z29"/>
+  <dimension ref="A1:AB29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -454,24 +456,26 @@
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="37" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="46" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="27" customWidth="1" min="20" max="20"/>
-    <col width="33" customWidth="1" min="21" max="21"/>
-    <col width="60" customWidth="1" min="22" max="22"/>
-    <col width="56" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="46" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="27" customWidth="1" min="22" max="22"/>
+    <col width="33" customWidth="1" min="23" max="23"/>
     <col width="60" customWidth="1" min="24" max="24"/>
-    <col width="40" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
+    <col width="56" customWidth="1" min="25" max="25"/>
+    <col width="60" customWidth="1" min="26" max="26"/>
+    <col width="40" customWidth="1" min="27" max="27"/>
+    <col width="25" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -517,90 +521,100 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>eye_style</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>scale_rule</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>hitbox_width</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>hitbox_height</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>hitbox_length</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>max_health</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>attack_damage</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>damage_text</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>movement_speed</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>flying_speed</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>follow_range</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>armor</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>knockback_resistance</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>breeding_item</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>immunities</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>behavior</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>spawns_text</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>drops_text</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>loot_table</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>sheet</t>
         </is>
@@ -645,62 +659,68 @@
           <t>minecraft:spider</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="n">
         <v>0.9</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0.5</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>1.1</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>14</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>3</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>3, plus Slowness I for 3 s</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>0.2</v>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
         <v>16</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
         <is>
           <t>Burrows under Regolith and waits; lunges when a player walks within 3 blocks</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Moon surface, groups of 1–3</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>Crawler Leg 0–2, Regolith Dust 1–3, rare Selenite shard</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/regolith_crawler</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>01_regolith_crawler.png</t>
         </is>
@@ -745,66 +765,72 @@
           <t>minecraft:armadillo</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
         <v>0.8</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.7</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>20</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>4</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>4 (horn ram) when provoked</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>0.2</v>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="n">
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
         <v>16</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>0</v>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>zerog_tweaks:rust_lichen</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
         <is>
           <t>Grazes on Rust Lichen; rams back when hit; tamed beetles with a Ferrox saddle carry a chest</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Mars plains, herds of 2–4</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>Beetle Grub 0–1, Ferrox bits 1–2, Rust Shell (armor upgrade)</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/rust_beetle</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>02_rust_beetle.png</t>
         </is>
@@ -849,66 +875,72 @@
           <t>minecraft:horse</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
         <v>0.9</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>1.8</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>1.3</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>20</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>0.33</v>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="n">
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
         <v>16</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>0</v>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>zerog_tweaks:starbloom</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
         <is>
           <t>Shear the antlers for 1–2 Starlite; they regrow over 5 minutes. Breeds with Starbloom</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Cerulon Azure Moss plains, herds of 3–5</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Stag Venison 1–3, Crystal Hide 0–2</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/crystal_stag</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>03_crystal_stag.png</t>
         </is>
@@ -953,58 +985,64 @@
           <t>minecraft:endermite</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ender_eye</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
         <v>0.5</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0.75</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
         <v>8</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>2</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>2</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>0.33</v>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="n">
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
         <v>16</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>0</v>
       </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
         <is>
           <t>Swarms in groups; shatters into 2–3 crystal shards on death that deal 1 damage nearby</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Cerulean geodes and crystal caves</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>Crystal shard 1–3 (smelts to Cerulite dust)</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/prismling</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>04_prismling.png</t>
         </is>
@@ -1049,66 +1087,72 @@
           <t>minecraft:wolf</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="n">
         <v>0.7</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0.9</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>1.2</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>18</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>4</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>4, sets target on fire for 2 s</t>
         </is>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>0.33</v>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="n">
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
         <v>24</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>0</v>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
         <is>
           <t>fire; lava</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Hunts in packs of 3–5; circles, then lunges together. Immune to fire</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Skarn Ember Crust fields</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>Cinder pelt, Emberite 0–2</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/cinder_hound</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>05_cinder_hound.png</t>
         </is>
@@ -1153,64 +1197,70 @@
           <t>minecraft:vindicator</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="n">
         <v>1</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>2.4</v>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
         <v>120</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>9</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>9; glaive sweep 12 and Slowness II</t>
         </is>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>0.2</v>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="n">
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
         <v>32</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>10</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>0.8</v>
       </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
         <is>
           <t>freezing</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>Guards the largest wrecks. Phase 2 at half health: summons 2 Rime Stalkers and an ice wall ring</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>One per large wreck on Eidolon; does not respawn</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>Wraithsteel Ingots 3–5, Frost Warden Helm (trophy), Remnant Shard</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/frost_warden</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>06_frost_warden.png</t>
         </is>
@@ -1255,66 +1305,72 @@
           <t>minecraft:vex</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ender_eye</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="n">
         <v>0.5</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0.5</v>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="n">
         <v>6</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>3</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>3 fire, or a small fireball at range</t>
         </is>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>0.33</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>16</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>0</v>
       </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
         <is>
           <t>fire; lava</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>Swarms around Flare Vents; bursts into flame when a vent erupts. Water puts it out instantly</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Solvane near Flare Vents, swarms of 4–8</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>Fusion Dust 0–1, Solar Spark</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/flare_sprite</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>07_flare_sprite.png</t>
         </is>
@@ -1359,64 +1415,70 @@
           <t>minecraft:iron_golem</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="n">
         <v>2.6</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>2.9</v>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="n">
         <v>200</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>14</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>14 slam; ground wave sets fire in a line</t>
         </is>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>0.15</v>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="n">
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="n">
         <v>32</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>20</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
         <is>
           <t>fire; lava</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>Wakes when a player steps on its Sunspot Rock plateau. Core opens to take damage after each slam</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>One per Solvane plateau structure</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>Astrium 4–6, Coronite 6–10, Colossus Core (Fusion Reactor upgrade)</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/sun_colossus</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>08_sun_colossus.png</t>
         </is>
@@ -1461,60 +1523,66 @@
           <t>minecraft:silverfish</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="n">
         <v>1.2</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>1.9</v>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="n">
         <v>40</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>8</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>8; can swallow and hold a player for 2 s</t>
         </is>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>0.33</v>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="n">
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
         <v>24</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>4</v>
       </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
         <v>0</v>
       </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr">
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
         <is>
           <t>Travels under sand shown as a moving ripple; bursts up under players who stand still</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Desert wastelands in every galaxy</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>Burrower Steak 1–3, Burrower Scale, Star Map Fragment (rare)</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/dune_burrower</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>09_dune_burrower.png</t>
         </is>
@@ -1559,68 +1627,74 @@
           <t>minecraft:strider</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ender_eye</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="n">
         <v>1</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>1.9</v>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="n">
         <v>30</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>6</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>6 stomp</t>
         </is>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>0.25</v>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="n">
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
         <v>16</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="n">
+      <c r="U11" t="n">
         <v>0</v>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>zerog_tweaks:cinder_cap</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>fire; lava</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>Wades across lava lakes; rideable with a saddle, making it the lava crossing mount</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Volcanic wastelands</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>Heatproof Plating (rare), ash 1–3</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/ash_strider</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>10_ash_strider.png</t>
         </is>
@@ -1665,64 +1739,70 @@
           <t>minecraft:ocelot</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="n">
         <v>0.8</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
         <v>24</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>5</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>5, plus Freezing</t>
         </is>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>0.33</v>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="n">
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
         <v>24</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0</v>
       </c>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
         <is>
           <t>freezing</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>Stalks from behind; only visible within 8 blocks during blizzards</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Frozen wastelands; summoned by the Frost Warden</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>Cryo Core (rare), Frost pelt</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/rime_stalker</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>11_rime_stalker.png</t>
         </is>
@@ -1767,66 +1847,72 @@
           <t>minecraft:axolotl</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>stalk</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="n">
         <v>1</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>0.7</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>1.4</v>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
         <v>28</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>5</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>5, and spits acid (Poison II, 4 s)</t>
         </is>
       </c>
-      <c r="O13" t="n">
+      <c r="Q13" t="n">
         <v>0.2</v>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="n">
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
         <v>16</v>
       </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>0</v>
       </c>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
         <is>
           <t>zerog_tweaks:acid; poison</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>Lies submerged in Acid with only eyes showing</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Toxic wastelands</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>Lurker Leg 1–2, Venom Gland 0–1, Neutralizer (rare)</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/bog_lurker</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>12_bog_lurker.png</t>
         </is>
@@ -1871,62 +1957,68 @@
           <t>minecraft:ghast</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ender_eye</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="n">
         <v>0.8</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>1.4</v>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
         <v>20</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>4</v>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>None unless hit, then 4</t>
         </is>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>0.2</v>
       </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>16</v>
       </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>0</v>
       </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr">
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
         <is>
           <t>Floats over craters; drops Meteorite Fragments as it drifts. Attacking one makes nearby drifters swarm</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>Barren wastelands</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>Stardust 1–2, Meteorite Fragment</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/crater_drifter</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>13_crater_drifter.png</t>
         </is>
@@ -1971,60 +2063,70 @@
           <t>minecraft:blaze</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ender_eye</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>6x player size: 3.6 wide, 10.8 tall</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>3.6</v>
+      </c>
       <c r="L15" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="n">
         <v>300</v>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>10</v>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>Light beams 10; shard spin 8</t>
         </is>
       </c>
-      <c r="O15" t="n">
+      <c r="Q15" t="n">
         <v>0.2</v>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="n">
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
         <v>48</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>15</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>1</v>
       </c>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr">
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
         <is>
           <t>1: beams bounce off the orbiting shards. 2: shards break loose and circle the arena. 3: core cracks open, and hits to the heart light deal double</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>Crystal amphitheater on Galaxy 2's key world</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>Galaxy 3 gate key, Cerulite 4–6, Sentinel Prism (T3 lens upgrade)</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/prism_sentinel</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>14_prism_sentinel.png</t>
         </is>
@@ -2069,62 +2171,70 @@
           <t>minecraft:ravager</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2.4</v>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>6x player size: 3.6 wide, 10.8 tall</t>
+        </is>
       </c>
       <c r="K16" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="L16" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
         <v>450</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>16</v>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>Claw 16; rift pull drags you toward the rift</t>
         </is>
       </c>
-      <c r="O16" t="n">
+      <c r="Q16" t="n">
         <v>0.25</v>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="n">
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
         <v>48</v>
       </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>18</v>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>1</v>
       </c>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr">
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
         <is>
           <t>1: charges and claws. 2: rift pulls chunks of the arena into the void. 3: spines fire void shards</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>Fractured island over the void on Galaxy 3's key world</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>Galaxy 4 gate key, Skarnite 4–6, Rift Heart</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/rift_tyrant</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>15_rift_tyrant.png</t>
         </is>
@@ -2169,60 +2279,70 @@
           <t>minecraft:vindicator</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>6x player size: 3.6 wide, 10.8 tall</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>400</v>
+      </c>
+      <c r="O17" t="n">
+        <v>13</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Cutlass 13; lantern beam chills</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>48</v>
+      </c>
+      <c r="T17" t="n">
+        <v>14</v>
+      </c>
+      <c r="U17" t="n">
         <v>0.9</v>
       </c>
-      <c r="J17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="n">
-        <v>400</v>
-      </c>
-      <c r="M17" t="n">
-        <v>13</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Cutlass 13; lantern beam chills</t>
-        </is>
-      </c>
-      <c r="O17" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="n">
-        <v>48</v>
-      </c>
-      <c r="R17" t="n">
-        <v>14</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr">
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
         <is>
           <t>1: duels with the cutlass. 2: calls Hollow Crewmen. 3: fleet lantern freezes the deck</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>Flagship deck on Galaxy 4's key world</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>Galaxy 5 gate key, Eidolite 4–6; Captain's Lantern if spared</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/eidolon_captain</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>16_eidolon_captain.png</t>
         </is>
@@ -2267,62 +2387,72 @@
           <t>minecraft:wither</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ender_eye</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>6x player size: 3.6 wide, 10.8 tall</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
         <v>3.6</v>
       </c>
-      <c r="J18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
         <v>900</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>20</v>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>Solar flare 20; falling stars 12</t>
         </is>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>0.2</v>
       </c>
-      <c r="P18" t="n">
+      <c r="R18" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>64</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>20</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>1</v>
       </c>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr">
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
         <is>
           <t>1: Vael fights from the surface. 2: corona rays sweep the arena. 3: the star collapses, the core opens and the arena shrinks</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>Floating ring platform above Solvane</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>Heart of Solvane, Solvanite 6–8, T6 crown</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/dying_star</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>17_dying_star.png</t>
         </is>
@@ -2367,64 +2497,70 @@
           <t>minecraft:rabbit</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="n">
         <v>0.5</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>0.6</v>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="n">
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
         <v>6</v>
       </c>
-      <c r="M19" t="n">
+      <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>0.25</v>
       </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="n">
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
         <v>16</v>
       </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="n">
+      <c r="U19" t="n">
         <v>0</v>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>zerog_tweaks:lunar_lichen</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
         <is>
           <t>Hops up to 4 blocks high in Moon gravity; flees when hit</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>Moon surface, groups of 2–4</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>Hopper Meat 0–2, Hopper Fluff 1–2</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/moon_hopper</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>18_moon_hopper.png</t>
         </is>
@@ -2469,64 +2605,70 @@
           <t>minecraft:cow</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="n">
         <v>1.3</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>1.4</v>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="n">
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="n">
         <v>24</v>
       </c>
-      <c r="M20" t="n">
+      <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
         <v>0.25</v>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="n">
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
         <v>16</v>
       </c>
-      <c r="R20" t="n">
+      <c r="T20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="n">
+      <c r="U20" t="n">
         <v>0</v>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>zerog_tweaks:rust_tuber</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
         <is>
           <t>Grazes in herds; the whole herd stampedes if one is hit</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>Mars plains, herds of 3–6</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>Grazer Steak 1–3, Grazer Hide 0–2</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/dust_grazer</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>19_dust_grazer.png</t>
         </is>
@@ -2571,64 +2713,70 @@
           <t>minecraft:chicken</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="n">
         <v>0.4</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>0.8</v>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="n">
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="n">
         <v>4</v>
       </c>
-      <c r="M21" t="n">
+      <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="O21" t="n">
+      <c r="Q21" t="n">
         <v>0.25</v>
       </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="n">
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
         <v>16</v>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="n">
+      <c r="U21" t="n">
         <v>0</v>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>zerog_tweaks:skyberries</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
         <is>
           <t>Glides slowly when falling; lays a Blue Egg every 5–10 minutes</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>Cerulon moss plains and Shardwood forests</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>Raw Fowl 1, Azure Feather 0–2</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/azure_fowl</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>20_azure_fowl.png</t>
         </is>
@@ -2673,60 +2821,66 @@
           <t>minecraft:tropical_fish</t>
         </is>
       </c>
-      <c r="I22" t="n">
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="n">
         <v>0.5</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>0.4</v>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="n">
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="n">
         <v>3</v>
       </c>
-      <c r="M22" t="n">
+      <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="O22" t="n">
+      <c r="Q22" t="n">
         <v>0.33</v>
       </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="n">
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
         <v>16</v>
       </c>
-      <c r="R22" t="n">
+      <c r="T22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="n">
+      <c r="U22" t="n">
         <v>0</v>
       </c>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr">
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
         <is>
           <t>Schools of 4–8; lights the water around it at night</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>Cerulon lakes and oceans</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>Glimmerfish 1, Glimmer Scale 0–1 (rare)</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/glimmerfish</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>21_glimmerfish.png</t>
         </is>
@@ -2771,70 +2925,76 @@
           <t>minecraft:hoglin</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="n">
         <v>0.9</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>0.9</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>1.3</v>
       </c>
-      <c r="L23" t="n">
+      <c r="N23" t="n">
         <v>26</v>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
         <v>6</v>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>6 charge, only when provoked</t>
         </is>
       </c>
-      <c r="O23" t="n">
+      <c r="Q23" t="n">
         <v>0.25</v>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="n">
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
         <v>16</v>
       </c>
-      <c r="R23" t="n">
+      <c r="T23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="n">
+      <c r="U23" t="n">
         <v>0</v>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>zerog_tweaks:cinder_cap</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>fire</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>Roots through Slag; charges if hit or if you get too close to its young</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>Skarn slag fields</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>Boar Chop 1–3, Boar Tusk 0–1</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/slag_boar</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>22_slag_boar.png</t>
         </is>
@@ -2879,66 +3039,72 @@
           <t>minecraft:parrot</t>
         </is>
       </c>
-      <c r="I24" t="n">
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="n">
         <v>0.6</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>0.6</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
+      <c r="N24" t="n">
         <v>16</v>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>3</v>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>3 bite; spits a fire bolt (3 + fire)</t>
         </is>
       </c>
-      <c r="O24" t="n">
+      <c r="Q24" t="n">
         <v>0.25</v>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="n">
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
         <v>16</v>
       </c>
-      <c r="R24" t="n">
+      <c r="T24" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
         <v>0</v>
       </c>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr">
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
         <is>
           <t>fire</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>Glides between ledges; guards Emberite veins</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>Skarn lava contact zones</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>Scorch Tail 1, Scorch Scale 0–2</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/scorch_wyrmling</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>23_scorch_wyrmling.png</t>
         </is>
@@ -2983,68 +3149,74 @@
           <t>minecraft:cow</t>
         </is>
       </c>
-      <c r="I25" t="n">
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="n">
         <v>1.4</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>1.7</v>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="n">
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="n">
         <v>30</v>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="O25" t="n">
+      <c r="Q25" t="n">
         <v>0.2</v>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="n">
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
         <v>16</v>
       </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="n">
+      <c r="U25" t="n">
         <v>0</v>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>zerog_tweaks:frostfern</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>freezing</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>Shear for Yak Wool; milk with a glass bottle for Frost Milk. Shelters calves in blizzards</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>Eidolon glaciers, herds of 2–4</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>Yak Meat 1–3, Yak Wool 1–2</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/frost_yak</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>24_frost_yak.png</t>
         </is>
@@ -3089,66 +3261,72 @@
           <t>minecraft:silverfish</t>
         </is>
       </c>
-      <c r="I26" t="n">
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="n">
         <v>0.6</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>0.4</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>1.2</v>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
         <v>14</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>2</v>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>2 and latches on: Hunger II while attached</t>
         </is>
       </c>
-      <c r="O26" t="n">
+      <c r="Q26" t="n">
         <v>0.25</v>
       </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="n">
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
         <v>16</v>
       </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="n">
+      <c r="U26" t="n">
         <v>0</v>
       </c>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr">
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
         <is>
           <t>freezing</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>Hides under Snowpack; shake it off by sprinting or hitting it</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>Eidolon snowfields and wreck interiors</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>Leech Gel 1–3</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/ice_leech</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>25_ice_leech.png</t>
         </is>
@@ -3193,68 +3371,74 @@
           <t>minecraft:spider</t>
         </is>
       </c>
-      <c r="I27" t="n">
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>stalk</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="n">
         <v>0.9</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>0.5</v>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="n">
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="n">
         <v>12</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>3</v>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>3 pinch, only when attacked</t>
         </is>
       </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
         <v>0.25</v>
       </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="n">
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
         <v>16</v>
       </c>
-      <c r="R27" t="n">
+      <c r="T27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="n">
+      <c r="U27" t="n">
         <v>0</v>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>zerog_tweaks:pyrefruit</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>fire; zerog_tweaks:corona_crust</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>Walks sideways; basks on Sunspot Rock and is immune to heat</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>Solvane Sunspot Rock shores</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>Gildcrab Meat 1–2, Gildcrab Shell 0–1</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/gildcrab</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>26_gildcrab.png</t>
         </is>
@@ -3299,62 +3483,68 @@
           <t>minecraft:dolphin</t>
         </is>
       </c>
-      <c r="I28" t="n">
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="n">
         <v>0.6</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>0.6</v>
       </c>
-      <c r="K28" t="n">
+      <c r="M28" t="n">
         <v>1.8</v>
       </c>
-      <c r="L28" t="n">
+      <c r="N28" t="n">
         <v>22</v>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>6</v>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>6 bite; pulls you down 2 blocks</t>
         </is>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
         <v>0.33</v>
       </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="n">
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
         <v>16</v>
       </c>
-      <c r="R28" t="n">
+      <c r="T28" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="n">
+      <c r="U28" t="n">
         <v>0</v>
       </c>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr">
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
         <is>
           <t>Lurks in trenches; follows light sources</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>Ocean wastelands in every galaxy (tinted)</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>Eel Fillet 1–2, Eel Skin 0–1</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/deep_eel</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>27_deep_eel.png</t>
         </is>
@@ -3399,76 +3589,3890 @@
           <t>minecraft:spider</t>
         </is>
       </c>
-      <c r="I29" t="n">
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="n">
         <v>1</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>0.6</v>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="n">
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="n">
         <v>16</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>3</v>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>3 and Poison I for 4 s</t>
         </is>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
         <v>0.33</v>
       </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="n">
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
         <v>16</v>
       </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="n">
+      <c r="U29" t="n">
         <v>0</v>
       </c>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr">
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
         <is>
           <t>poison</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>Buries itself in Dunesand; bursts out in groups of 2–3</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>Desert wastelands (tinted)</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>Skitter Leg 1–2, Skitter Carapace 0–1, Venom Gland 0–1</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>zerog_tweaks:entities/sand_skitter</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>28_sand_skitter.png</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z29"/>
+  <autoFilter ref="A1:AB29"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D118"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>mob</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>animation</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>exists</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>loop</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>regolith_crawler</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>animation.regolith_crawler.idle</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>regolith_crawler</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>animation.regolith_crawler.walk</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>regolith_crawler</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>animation.regolith_crawler.burrow</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>regolith_crawler</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>animation.regolith_crawler.emerge</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>regolith_crawler</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>animation.regolith_crawler.lunge</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>regolith_crawler</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>animation.regolith_crawler.death</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>rust_beetle</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>animation.rust_beetle.idle</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>rust_beetle</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>animation.rust_beetle.walk</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>rust_beetle</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>animation.rust_beetle.ram</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>rust_beetle</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>animation.rust_beetle.hop</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>rust_beetle</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>animation.rust_beetle.graze</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>crystal_stag</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>animation.crystal_stag.idle</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>crystal_stag</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>animation.crystal_stag.walk</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>crystal_stag</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>animation.crystal_stag.run</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>crystal_stag</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>animation.crystal_stag.graze</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>prismling</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>animation.prismling.idle</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>prismling</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>animation.prismling.walk</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>prismling</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>animation.prismling.attack</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>prismling</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>animation.prismling.shatter</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cinder_hound</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>animation.cinder_hound.idle</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cinder_hound</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>animation.cinder_hound.walk</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cinder_hound</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>animation.cinder_hound.run</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cinder_hound</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>animation.cinder_hound.lunge</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cinder_hound</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>animation.cinder_hound.bite</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>frost_warden</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>animation.frost_warden.idle</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>frost_warden</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>animation.frost_warden.walk</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>frost_warden</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>animation.frost_warden.sweep</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>frost_warden</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>animation.frost_warden.summon</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>frost_warden</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>animation.frost_warden.death</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>flare_sprite</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>animation.flare_sprite.fly</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>flare_sprite</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>animation.flare_sprite.attack</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>sun_colossus</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>animation.sun_colossus.dormant</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>sun_colossus</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>animation.sun_colossus.wake</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>sun_colossus</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>animation.sun_colossus.walk</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>sun_colossus</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>animation.sun_colossus.slam</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>sun_colossus</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>animation.sun_colossus.core_open</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>sun_colossus</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>animation.sun_colossus.death</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>dune_burrower</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>animation.dune_burrower.burrow</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>dune_burrower</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>animation.dune_burrower.burst</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>dune_burrower</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>animation.dune_burrower.swallow</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>dune_burrower</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>animation.dune_burrower.walk</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>dune_burrower</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>animation.dune_burrower.attack</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ash_strider</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>animation.ash_strider.idle</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ash_strider</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>animation.ash_strider.walk</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ash_strider</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>animation.ash_strider.stomp</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>rime_stalker</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>animation.rime_stalker.idle</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>rime_stalker</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>animation.rime_stalker.walk</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>rime_stalker</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>animation.rime_stalker.pounce</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>rime_stalker</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>animation.rime_stalker.attack</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>bog_lurker</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>animation.bog_lurker.idle</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>bog_lurker</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>animation.bog_lurker.walk</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>bog_lurker</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>animation.bog_lurker.swim</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>bog_lurker</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>animation.bog_lurker.spit</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>crater_drifter</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>animation.crater_drifter.float</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>crater_drifter</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>animation.crater_drifter.attack</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>prism_sentinel</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>animation.prism_sentinel.idle</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>prism_sentinel</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>animation.prism_sentinel.beam</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>prism_sentinel</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>animation.prism_sentinel.shard_spin</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>prism_sentinel</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>animation.prism_sentinel.core_open</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>prism_sentinel</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>animation.prism_sentinel.death</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>rift_tyrant</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>animation.rift_tyrant.idle</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>rift_tyrant</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>animation.rift_tyrant.walk</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>rift_tyrant</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>animation.rift_tyrant.charge</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>rift_tyrant</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>animation.rift_tyrant.claw</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>rift_tyrant</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>animation.rift_tyrant.roar</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>rift_tyrant</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>animation.rift_tyrant.shard_volley</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>rift_tyrant</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>animation.rift_tyrant.death</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>eidolon_captain</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>animation.eidolon_captain.idle</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>eidolon_captain</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>animation.eidolon_captain.walk</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>eidolon_captain</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>animation.eidolon_captain.slash</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>eidolon_captain</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>animation.eidolon_captain.summon</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>eidolon_captain</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>animation.eidolon_captain.lantern</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>eidolon_captain</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>animation.eidolon_captain.yield</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>eidolon_captain</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>animation.eidolon_captain.death</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>dying_star</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>animation.dying_star.idle</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>dying_star</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>animation.dying_star.flare</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>dying_star</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>animation.dying_star.sweep</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>dying_star</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>animation.dying_star.collapse</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>dying_star</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>animation.dying_star.death</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>moon_hopper</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>animation.moon_hopper.idle</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>moon_hopper</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>animation.moon_hopper.hop</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>moon_hopper</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>animation.moon_hopper.graze</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>dust_grazer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>animation.dust_grazer.idle</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>dust_grazer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>animation.dust_grazer.walk</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>dust_grazer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>animation.dust_grazer.run</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>dust_grazer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>animation.dust_grazer.graze</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>azure_fowl</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>animation.azure_fowl.idle</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>azure_fowl</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>animation.azure_fowl.walk</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>azure_fowl</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>animation.azure_fowl.glide</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>azure_fowl</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>animation.azure_fowl.flap</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>glimmerfish</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>animation.glimmerfish.swim</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>glimmerfish</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>animation.glimmerfish.flop</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>slag_boar</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>animation.slag_boar.idle</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>slag_boar</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>animation.slag_boar.walk</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>slag_boar</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>animation.slag_boar.charge</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>slag_boar</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>animation.slag_boar.root</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>scorch_wyrmling</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>animation.scorch_wyrmling.idle</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>scorch_wyrmling</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>animation.scorch_wyrmling.walk</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>scorch_wyrmling</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>animation.scorch_wyrmling.glide</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>scorch_wyrmling</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>animation.scorch_wyrmling.spit</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>scorch_wyrmling</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>animation.scorch_wyrmling.bite</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>frost_yak</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>animation.frost_yak.idle</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>frost_yak</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>animation.frost_yak.walk</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>frost_yak</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>animation.frost_yak.graze</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>ice_leech</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>animation.ice_leech.idle</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>ice_leech</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>animation.ice_leech.crawl</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>ice_leech</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>animation.ice_leech.latch</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>gildcrab</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>animation.gildcrab.idle</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>gildcrab</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>animation.gildcrab.walk_sideways</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>gildcrab</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>animation.gildcrab.pinch</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>gildcrab</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>animation.gildcrab.bask</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>deep_eel</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>animation.deep_eel.swim</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>deep_eel</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>animation.deep_eel.bite</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>sand_skitter</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>animation.sand_skitter.idle</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>sand_skitter</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>animation.sand_skitter.walk</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>sand_skitter</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>animation.sand_skitter.burst</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>sand_skitter</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>animation.sand_skitter.sting</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D118"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="37" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>mob</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>mod</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>eye_style</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>scale</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>regolith_crawler</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Regolith Crawler</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>zerog_tweaks</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>rust_beetle</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rust Beetle</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>zerog_tweaks</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>crystal_stag</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Crystal Stag</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>zerog_tweaks</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>prismling</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Prismling</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>zerog_tweaks</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ender_eye</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cinder_hound</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cinder Hound</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>zerog_tweaks</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>frost_warden</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Frost Warden</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>zerog_tweaks</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>flare_sprite</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Flare Sprite</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>zerog_tweaks</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ender_eye</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sun_colossus</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sun Colossus</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>zerog_tweaks</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>dune_burrower</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dune Burrower</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>zerog_tweaks</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ash_strider</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ash Strider</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>zerog_tweaks</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ender_eye</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>rime_stalker</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rime Stalker</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>zerog_tweaks</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>bog_lurker</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Bog Lurker</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>zerog_tweaks</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>stalk</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>crater_drifter</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Crater Drifter</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>zerog_tweaks</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ender_eye</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>prism_sentinel</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Prism Sentinel</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>zerog_tweaks</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ender_eye</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>6x player size: 3.6 wide, 10.8 tall</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>rift_tyrant</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rift Tyrant</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>zerog_tweaks</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>6x player size: 3.6 wide, 10.8 tall</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>eidolon_captain</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Eidolon Captain</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>zerog_tweaks</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>6x player size: 3.6 wide, 10.8 tall</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>dying_star</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>The Dying Star</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>zerog_tweaks</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ender_eye</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>6x player size: 3.6 wide, 10.8 tall</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>moon_hopper</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Moon Hopper</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>zerog_tweaks</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>dust_grazer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dust Grazer</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>zerog_tweaks</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>azure_fowl</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Azure Fowl</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>zerog_tweaks</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>glimmerfish</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Glimmerfish</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>zerog_tweaks</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>slag_boar</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Slag Boar</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>zerog_tweaks</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>scorch_wyrmling</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Scorch Wyrmling</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>zerog_tweaks</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>frost_yak</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Frost Yak</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>zerog_tweaks</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ice_leech</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Ice Leech</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>zerog_tweaks</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>gildcrab</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Gildcrab</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>zerog_tweaks</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>stalk</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>deep_eel</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Deep Eel</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>zerog_tweaks</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sand_skitter</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Sand Skitter</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>zerog_tweaks</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>mossback</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Mossback</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>shattered_skies</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>amethyst_stalker</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Amethyst Stalker</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>shattered_skies</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>meteor_maw</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Meteor Maw</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>shattered_skies</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>tidewraith</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Tidewraith</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>shattered_skies</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Build it on the vanilla Phantom model: same rig and flight animations, retextured with pixel scales and manta-ray gill slits on the underside.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>hollow_sentinel</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Hollow Sentinel</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>shattered_skies</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>stormbitten_wyvern</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Stormbitten Wyvern</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>shattered_skies</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>splinter_mite</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Splinter Mite</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>shattered_skies</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ender_eye</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Listed as "Splinter": applied to both Splinter adds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>splinter_wisp</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Splinter Wisp</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>shattered_skies</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ender_eye</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Listed as "Splinter": applied to both Splinter adds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>shardmother</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Shardmother</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>shattered_skies</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>stalk</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>slagjaw</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Slagjaw</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>shattered_skies</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G39"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4253,7 +8257,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6870,7 +10874,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7671,7 +11675,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10409,7 +14413,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11152,7 +15156,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13739,7 +17743,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17104,2621 +21108,4 @@
   <autoFilter ref="A1:D153"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D118"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>mob</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>animation</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>exists</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>loop</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>regolith_crawler</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>animation.regolith_crawler.idle</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>regolith_crawler</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>animation.regolith_crawler.walk</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>regolith_crawler</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>animation.regolith_crawler.burrow</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>regolith_crawler</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>animation.regolith_crawler.emerge</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>regolith_crawler</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>animation.regolith_crawler.lunge</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>regolith_crawler</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>animation.regolith_crawler.death</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>rust_beetle</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>animation.rust_beetle.idle</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>rust_beetle</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>animation.rust_beetle.walk</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>rust_beetle</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>animation.rust_beetle.ram</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>rust_beetle</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>animation.rust_beetle.hop</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>rust_beetle</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>animation.rust_beetle.graze</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>crystal_stag</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>animation.crystal_stag.idle</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>crystal_stag</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>animation.crystal_stag.walk</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>crystal_stag</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>animation.crystal_stag.run</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>crystal_stag</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>animation.crystal_stag.graze</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>prismling</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>animation.prismling.idle</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>prismling</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>animation.prismling.walk</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>prismling</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>animation.prismling.attack</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>prismling</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>animation.prismling.shatter</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>cinder_hound</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>animation.cinder_hound.idle</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>cinder_hound</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>animation.cinder_hound.walk</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>cinder_hound</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>animation.cinder_hound.run</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>cinder_hound</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>animation.cinder_hound.lunge</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>cinder_hound</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>animation.cinder_hound.bite</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>frost_warden</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>animation.frost_warden.idle</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>frost_warden</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>animation.frost_warden.walk</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>frost_warden</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>animation.frost_warden.sweep</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>frost_warden</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>animation.frost_warden.summon</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>frost_warden</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>animation.frost_warden.death</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>flare_sprite</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>animation.flare_sprite.fly</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>flare_sprite</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>animation.flare_sprite.attack</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>sun_colossus</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>animation.sun_colossus.dormant</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>sun_colossus</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>animation.sun_colossus.wake</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>sun_colossus</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>animation.sun_colossus.walk</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>sun_colossus</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>animation.sun_colossus.slam</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>sun_colossus</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>animation.sun_colossus.core_open</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>sun_colossus</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>animation.sun_colossus.death</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>dune_burrower</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>animation.dune_burrower.burrow</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>dune_burrower</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>animation.dune_burrower.burst</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>dune_burrower</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>animation.dune_burrower.swallow</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>dune_burrower</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>animation.dune_burrower.walk</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>dune_burrower</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>animation.dune_burrower.attack</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>ash_strider</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>animation.ash_strider.idle</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>ash_strider</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>animation.ash_strider.walk</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>ash_strider</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>animation.ash_strider.stomp</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>rime_stalker</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>animation.rime_stalker.idle</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>rime_stalker</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>animation.rime_stalker.walk</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>rime_stalker</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>animation.rime_stalker.pounce</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>rime_stalker</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>animation.rime_stalker.attack</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>bog_lurker</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>animation.bog_lurker.idle</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>bog_lurker</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>animation.bog_lurker.walk</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>bog_lurker</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>animation.bog_lurker.swim</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>bog_lurker</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>animation.bog_lurker.spit</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>crater_drifter</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>animation.crater_drifter.float</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>crater_drifter</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>animation.crater_drifter.attack</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>prism_sentinel</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>animation.prism_sentinel.idle</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>prism_sentinel</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>animation.prism_sentinel.beam</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>prism_sentinel</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>animation.prism_sentinel.shard_spin</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>prism_sentinel</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>animation.prism_sentinel.core_open</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>prism_sentinel</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>animation.prism_sentinel.death</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>rift_tyrant</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>animation.rift_tyrant.idle</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>rift_tyrant</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>animation.rift_tyrant.walk</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>rift_tyrant</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>animation.rift_tyrant.charge</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>rift_tyrant</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>animation.rift_tyrant.claw</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>rift_tyrant</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>animation.rift_tyrant.roar</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>rift_tyrant</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>animation.rift_tyrant.shard_volley</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>rift_tyrant</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>animation.rift_tyrant.death</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>eidolon_captain</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>animation.eidolon_captain.idle</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>eidolon_captain</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>animation.eidolon_captain.walk</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>eidolon_captain</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>animation.eidolon_captain.slash</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>eidolon_captain</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>animation.eidolon_captain.summon</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>eidolon_captain</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>animation.eidolon_captain.lantern</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>eidolon_captain</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>animation.eidolon_captain.yield</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>eidolon_captain</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>animation.eidolon_captain.death</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>dying_star</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>animation.dying_star.idle</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>dying_star</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>animation.dying_star.flare</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>dying_star</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>animation.dying_star.sweep</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>dying_star</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>animation.dying_star.collapse</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>dying_star</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>animation.dying_star.death</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>moon_hopper</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>animation.moon_hopper.idle</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>moon_hopper</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>animation.moon_hopper.hop</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>moon_hopper</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>animation.moon_hopper.graze</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>dust_grazer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>animation.dust_grazer.idle</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>dust_grazer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>animation.dust_grazer.walk</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>dust_grazer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>animation.dust_grazer.run</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>dust_grazer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>animation.dust_grazer.graze</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>azure_fowl</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>animation.azure_fowl.idle</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>azure_fowl</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>animation.azure_fowl.walk</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>azure_fowl</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>animation.azure_fowl.glide</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>azure_fowl</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>animation.azure_fowl.flap</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>glimmerfish</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>animation.glimmerfish.swim</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>glimmerfish</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>animation.glimmerfish.flop</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>slag_boar</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>animation.slag_boar.idle</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>slag_boar</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>animation.slag_boar.walk</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>slag_boar</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>animation.slag_boar.charge</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>slag_boar</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>animation.slag_boar.root</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>scorch_wyrmling</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>animation.scorch_wyrmling.idle</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>scorch_wyrmling</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>animation.scorch_wyrmling.walk</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>scorch_wyrmling</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>animation.scorch_wyrmling.glide</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>scorch_wyrmling</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>animation.scorch_wyrmling.spit</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>scorch_wyrmling</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>animation.scorch_wyrmling.bite</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>frost_yak</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>animation.frost_yak.idle</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>frost_yak</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>animation.frost_yak.walk</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>frost_yak</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>animation.frost_yak.graze</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>ice_leech</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>animation.ice_leech.idle</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>ice_leech</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>animation.ice_leech.crawl</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>ice_leech</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>animation.ice_leech.latch</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>gildcrab</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>animation.gildcrab.idle</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>gildcrab</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>animation.gildcrab.walk_sideways</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>gildcrab</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>animation.gildcrab.pinch</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>gildcrab</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>animation.gildcrab.bask</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>deep_eel</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>animation.deep_eel.swim</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>deep_eel</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>animation.deep_eel.bite</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>sand_skitter</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>animation.sand_skitter.idle</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>sand_skitter</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>animation.sand_skitter.walk</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>sand_skitter</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>animation.sand_skitter.burst</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>sand_skitter</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>animation.sand_skitter.sting</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:D118"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>